--- a/exports/trend_1d/KEI_full_report.xlsx
+++ b/exports/trend_1d/KEI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.14</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42087</v>
+        <v>42088</v>
       </c>
       <c r="H2" t="n">
-        <v>58.65</v>
+        <v>57.45</v>
       </c>
       <c r="I2" t="n">
         <v>57.73537046279132</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>8.210000000000001</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>5.17</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>17.05</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42100</v>
+        <v>42101</v>
       </c>
       <c r="H3" t="n">
-        <v>64.95</v>
+        <v>77.3</v>
       </c>
       <c r="I3" t="n">
         <v>65.6252620413205</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.05</v>
+        <v>-34.55</v>
       </c>
       <c r="L3" t="n">
-        <v>13.73</v>
+        <v>35.6</v>
       </c>
       <c r="M3" t="n">
         <v>11.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5.29</v>
+        <v>19.01</v>
       </c>
       <c r="O3" t="n">
         <v>-2.05</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>25.08</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>73.55</v>
+        <v>67.55</v>
       </c>
       <c r="I4" t="n">
         <v>69.45331467803075</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.85</v>
+        <v>-12.61</v>
       </c>
       <c r="L4" t="n">
         <v>17.59</v>
@@ -669,7 +716,7 @@
         <v>1.2</v>
       </c>
       <c r="N4" t="n">
-        <v>7.28</v>
+        <v>8.16</v>
       </c>
       <c r="O4" t="n">
         <v>19.01</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>28.1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42185</v>
+        <v>42186</v>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>73.05</v>
       </c>
       <c r="I5" t="n">
         <v>72.67769849122639</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.63</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>16.71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>11.43</v>
       </c>
       <c r="N5" t="n">
         <v>5.34</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.45</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>102.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>98.86599997840557</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" t="n">
-        <v>40.73</v>
+        <v>33.33</v>
       </c>
       <c r="L6" t="n">
         <v>5.42</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>24.3</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42327</v>
+        <v>42328</v>
       </c>
       <c r="H7" t="n">
-        <v>103.85</v>
+        <v>113.2</v>
       </c>
       <c r="I7" t="n">
         <v>112.4850909527362</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.62</v>
+        <v>-16.22</v>
       </c>
       <c r="L7" t="n">
         <v>24.64</v>
@@ -840,7 +923,7 @@
         <v>6.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.470000000000001</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
         <v>-5.25</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>17.19</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>112.55</v>
+        <v>103.2</v>
       </c>
       <c r="I8" t="n">
         <v>107.3507205263637</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.57</v>
+        <v>-8.83</v>
       </c>
       <c r="L8" t="n">
-        <v>11.97</v>
+        <v>13.25</v>
       </c>
       <c r="M8" t="n">
         <v>3.72</v>
       </c>
       <c r="N8" t="n">
-        <v>6.49</v>
+        <v>8.31</v>
       </c>
       <c r="O8" t="n">
         <v>9</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>17.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H9" t="n">
-        <v>102.15</v>
+        <v>106.05</v>
       </c>
       <c r="I9" t="n">
         <v>104.9787158115884</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>1.02</v>
+        <v>-2.76</v>
       </c>
       <c r="L9" t="n">
         <v>9.5</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.29</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42531</v>
+        <v>42534</v>
       </c>
       <c r="H10" t="n">
-        <v>103.95</v>
+        <v>102.5</v>
       </c>
       <c r="I10" t="n">
         <v>103.8313983146955</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.98</v>
+        <v>-3.35</v>
       </c>
       <c r="L10" t="n">
         <v>4.76</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42550</v>
+        <v>42551</v>
       </c>
       <c r="H11" t="n">
-        <v>108</v>
+        <v>112.15</v>
       </c>
       <c r="I11" t="n">
         <v>110.8910479565528</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.37</v>
+        <v>-9.41</v>
       </c>
       <c r="L11" t="n">
-        <v>6.88</v>
+        <v>9.76</v>
       </c>
       <c r="M11" t="n">
         <v>1.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.86</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42593</v>
+        <v>42594</v>
       </c>
       <c r="H12" t="n">
-        <v>113</v>
+        <v>111.95</v>
       </c>
       <c r="I12" t="n">
         <v>112.8888878398349</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>0.76</v>
+        <v>-0.18</v>
       </c>
       <c r="L12" t="n">
         <v>3.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.63</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42678</v>
+        <v>42681</v>
       </c>
       <c r="H13" t="n">
-        <v>114.75</v>
+        <v>124</v>
       </c>
       <c r="I13" t="n">
         <v>122.7208935260437</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5</v>
+        <v>-10.76</v>
       </c>
       <c r="L13" t="n">
-        <v>10.94</v>
+        <v>13.89</v>
       </c>
       <c r="M13" t="n">
         <v>5.53</v>
       </c>
       <c r="N13" t="n">
-        <v>6.66</v>
+        <v>8.06</v>
       </c>
       <c r="O13" t="n">
         <v>-0.93</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42692</v>
+        <v>42695</v>
       </c>
       <c r="H14" t="n">
-        <v>116.45</v>
+        <v>110.05</v>
       </c>
       <c r="I14" t="n">
         <v>111.918088613586</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.09</v>
+        <v>-11.25</v>
       </c>
       <c r="L14" t="n">
         <v>14.44</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>28.7</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H15" t="n">
-        <v>126.05</v>
+        <v>134.9</v>
       </c>
       <c r="I15" t="n">
         <v>133.5135299429247</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.54</v>
+        <v>-22.58</v>
       </c>
       <c r="L15" t="n">
-        <v>18.76</v>
+        <v>26.03</v>
       </c>
       <c r="M15" t="n">
         <v>5.62</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H16" t="n">
-        <v>213.55</v>
+        <v>203.5</v>
       </c>
       <c r="I16" t="n">
         <v>210.87530471878</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K16" t="n">
-        <v>58.3</v>
+        <v>50.85</v>
       </c>
       <c r="L16" t="n">
         <v>6.86</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>14.17</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42907</v>
+        <v>42908</v>
       </c>
       <c r="H17" t="n">
-        <v>221.9</v>
+        <v>230.2</v>
       </c>
       <c r="I17" t="n">
         <v>225.384305865606</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.039999999999999</v>
+        <v>-13.12</v>
       </c>
       <c r="L17" t="n">
-        <v>12.68</v>
+        <v>14.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.33</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>10.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H18" t="n">
-        <v>215.4</v>
+        <v>209.4</v>
       </c>
       <c r="I18" t="n">
         <v>212.4311073981785</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.43</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>8.25</v>
+        <v>10.51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="N18" t="n">
         <v>2.8</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>11.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42971</v>
+        <v>42975</v>
       </c>
       <c r="H19" t="n">
-        <v>233.25</v>
+        <v>245.35</v>
       </c>
       <c r="I19" t="n">
         <v>234.3086429311803</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.39</v>
+        <v>-17.17</v>
       </c>
       <c r="L19" t="n">
-        <v>13.18</v>
+        <v>18.22</v>
       </c>
       <c r="M19" t="n">
         <v>1.98</v>
       </c>
       <c r="N19" t="n">
-        <v>3.99</v>
+        <v>5.19</v>
       </c>
       <c r="O19" t="n">
         <v>-2.79</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.84</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H20" t="n">
-        <v>358.95</v>
+        <v>356.55</v>
       </c>
       <c r="I20" t="n">
         <v>356.6548936943912</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K20" t="n">
-        <v>46.3</v>
+        <v>45.32</v>
       </c>
       <c r="L20" t="n">
         <v>5.24</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.86</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43112</v>
+        <v>43115</v>
       </c>
       <c r="H21" t="n">
-        <v>406.45</v>
+        <v>410.45</v>
       </c>
       <c r="I21" t="n">
         <v>407.4269115665435</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>-14</v>
+        <v>-15.12</v>
       </c>
       <c r="L21" t="n">
         <v>18.08</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>11.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H22" t="n">
-        <v>367.8</v>
+        <v>351.85</v>
       </c>
       <c r="I22" t="n">
         <v>365.133072197018</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.39</v>
+        <v>-14.28</v>
       </c>
       <c r="L22" t="n">
-        <v>13.27</v>
+        <v>19.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.28</v>
+        <v>4.84</v>
       </c>
       <c r="N22" t="n">
         <v>6.83</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>15.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H23" t="n">
-        <v>385</v>
+        <v>400.9</v>
       </c>
       <c r="I23" t="n">
         <v>395.8377823919016</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.42</v>
+        <v>-13.94</v>
       </c>
       <c r="L23" t="n">
-        <v>13.54</v>
+        <v>15.53</v>
       </c>
       <c r="M23" t="n">
         <v>2.92</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10.76</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H24" t="n">
-        <v>454.45</v>
+        <v>387.95</v>
       </c>
       <c r="I24" t="n">
         <v>434.0419303969604</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K24" t="n">
-        <v>13.36</v>
+        <v>-3.23</v>
       </c>
       <c r="L24" t="n">
-        <v>3.26</v>
+        <v>7.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="N24" t="n">
-        <v>5.66</v>
+        <v>14.63</v>
       </c>
       <c r="O24" t="n">
         <v>4.13</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>25.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H25" t="n">
-        <v>435.4</v>
+        <v>452.5</v>
       </c>
       <c r="I25" t="n">
         <v>441.4503322310836</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" t="n">
-        <v>-12.23</v>
+        <v>-16.64</v>
       </c>
       <c r="L25" t="n">
-        <v>16.48</v>
+        <v>17.66</v>
       </c>
       <c r="M25" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="N25" t="n">
         <v>6.41</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>11.39</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43321</v>
+        <v>43322</v>
       </c>
       <c r="H26" t="n">
-        <v>427.15</v>
+        <v>403.05</v>
       </c>
       <c r="I26" t="n">
         <v>409.3316966182927</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.6</v>
+        <v>-10.93</v>
       </c>
       <c r="L26" t="n">
-        <v>6.24</v>
+        <v>11.36</v>
       </c>
       <c r="M26" t="n">
-        <v>0.67</v>
+        <v>4.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.55</v>
+        <v>5.64</v>
       </c>
       <c r="O26" t="n">
         <v>3.93</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>13.65</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H27" t="n">
-        <v>308.25</v>
+        <v>349.7</v>
       </c>
       <c r="I27" t="n">
         <v>314.3439265000947</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K27" t="n">
-        <v>23.52</v>
+        <v>13.24</v>
       </c>
       <c r="L27" t="n">
         <v>6.19</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>4.62</v>
       </c>
       <c r="N27" t="n">
-        <v>6.35</v>
+        <v>13.45</v>
       </c>
       <c r="O27" t="n">
         <v>-5.64</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>21.19</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H28" t="n">
-        <v>346.4</v>
+        <v>339.65</v>
       </c>
       <c r="I28" t="n">
         <v>342.0919275500113</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.87</v>
       </c>
       <c r="L28" t="n">
         <v>7.78</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>11.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H29" t="n">
-        <v>342.1</v>
+        <v>352.25</v>
       </c>
       <c r="I29" t="n">
         <v>348.7117342225596</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.72</v>
+        <v>-3.71</v>
       </c>
       <c r="L29" t="n">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="M29" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="N29" t="n">
         <v>6.14</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.03</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H30" t="n">
-        <v>394.05</v>
+        <v>372.6</v>
       </c>
       <c r="I30" t="n">
         <v>380.9122275371541</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
-        <v>11.87</v>
+        <v>5.78</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
@@ -2151,7 +2510,7 @@
         <v>1.33</v>
       </c>
       <c r="N30" t="n">
-        <v>5.19</v>
+        <v>5.44</v>
       </c>
       <c r="O30" t="n">
         <v>2.97</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43605</v>
+        <v>43606</v>
       </c>
       <c r="H31" t="n">
-        <v>409.45</v>
+        <v>416.65</v>
       </c>
       <c r="I31" t="n">
         <v>411.1349834251961</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.890000000000001</v>
+        <v>-11.82</v>
       </c>
       <c r="L31" t="n">
-        <v>11.23</v>
+        <v>13.53</v>
       </c>
       <c r="M31" t="n">
         <v>2.58</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.12</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43628</v>
+        <v>43629</v>
       </c>
       <c r="H32" t="n">
-        <v>468.5</v>
+        <v>455.2</v>
       </c>
       <c r="I32" t="n">
         <v>458.8988555589943</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>12.44</v>
+        <v>9.25</v>
       </c>
       <c r="L32" t="n">
         <v>1.07</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43683</v>
+        <v>43684</v>
       </c>
       <c r="H33" t="n">
-        <v>440.4</v>
+        <v>465.2</v>
       </c>
       <c r="I33" t="n">
         <v>464.3364391690779</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>-2.2</v>
       </c>
       <c r="L33" t="n">
         <v>8.19</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>15.18</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43698</v>
+        <v>43699</v>
       </c>
       <c r="H34" t="n">
-        <v>460.1</v>
+        <v>415.95</v>
       </c>
       <c r="I34" t="n">
         <v>421.6242510350512</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.1</v>
+        <v>-10.59</v>
       </c>
       <c r="L34" t="n">
-        <v>4.1</v>
+        <v>16.1</v>
       </c>
       <c r="M34" t="n">
         <v>1.16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="O34" t="n">
         <v>5.63</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>20.93</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H35" t="n">
-        <v>455.4</v>
+        <v>503.35</v>
       </c>
       <c r="I35" t="n">
         <v>502.9961137806814</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.48</v>
+        <v>-21.01</v>
       </c>
       <c r="L35" t="n">
-        <v>17.44</v>
+        <v>21.41</v>
       </c>
       <c r="M35" t="n">
         <v>1.75</v>
       </c>
       <c r="N35" t="n">
-        <v>8.41</v>
+        <v>10.53</v>
       </c>
       <c r="O35" t="n">
         <v>-9.6</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.22</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H36" t="n">
-        <v>546.15</v>
+        <v>525.5</v>
       </c>
       <c r="I36" t="n">
         <v>539.4579214746914</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
         <v>9.609999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.11</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43837</v>
+        <v>43838</v>
       </c>
       <c r="H37" t="n">
-        <v>471</v>
+        <v>489.6</v>
       </c>
       <c r="I37" t="n">
         <v>483.1270753894047</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K37" t="n">
-        <v>10.37</v>
+        <v>6.83</v>
       </c>
       <c r="L37" t="n">
         <v>10.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>13.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H38" t="n">
-        <v>509.9</v>
+        <v>490.5</v>
       </c>
       <c r="I38" t="n">
         <v>503.8941490415668</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K38" t="n">
-        <v>4.15</v>
+        <v>0.18</v>
       </c>
       <c r="L38" t="n">
         <v>6.05</v>
       </c>
       <c r="M38" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="N38" t="n">
         <v>3.83</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.63</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H39" t="n">
-        <v>293.05</v>
+        <v>307.7</v>
       </c>
       <c r="I39" t="n">
         <v>295.4753449249133</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K39" t="n">
-        <v>40.25</v>
+        <v>37.27</v>
       </c>
       <c r="L39" t="n">
         <v>6.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.93</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H40" t="n">
-        <v>379</v>
+        <v>369.6</v>
       </c>
       <c r="I40" t="n">
         <v>376.2938004734075</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K40" t="n">
-        <v>23.17</v>
+        <v>20.12</v>
       </c>
       <c r="L40" t="n">
         <v>3.48</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.38</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H41" t="n">
-        <v>356.1</v>
+        <v>365.1</v>
       </c>
       <c r="I41" t="n">
         <v>356.5953973492897</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>1.22</v>
       </c>
       <c r="L41" t="n">
         <v>5.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H42" t="n">
-        <v>887.55</v>
+        <v>810.25</v>
       </c>
       <c r="I42" t="n">
         <v>864.4367717533767</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K42" t="n">
-        <v>143.1</v>
+        <v>121.93</v>
       </c>
       <c r="L42" t="n">
         <v>3.46</v>
@@ -2835,7 +3338,7 @@
         <v>2.83</v>
       </c>
       <c r="N42" t="n">
-        <v>6.78</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O42" t="n">
         <v>2.53</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>230</v>
+        <v>231</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>12</v>
+      </c>
+      <c r="U42" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>27.7</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44515</v>
+        <v>44516</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.6</v>
+        <v>1036.75</v>
       </c>
       <c r="I43" t="n">
         <v>1034.711140943789</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-26.83</v>
+        <v>-27.95</v>
       </c>
       <c r="L43" t="n">
         <v>30.43</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.62</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44589</v>
+        <v>44592</v>
       </c>
       <c r="H44" t="n">
-        <v>1089.55</v>
+        <v>1076.2</v>
       </c>
       <c r="I44" t="n">
         <v>1081.667314843086</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K44" t="n">
-        <v>5.09</v>
+        <v>3.81</v>
       </c>
       <c r="L44" t="n">
         <v>5.28</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>14.87</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H45" t="n">
-        <v>1004.25</v>
+        <v>1131.55</v>
       </c>
       <c r="I45" t="n">
         <v>1122.398150002232</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K45" t="n">
-        <v>6.69</v>
+        <v>-5.14</v>
       </c>
       <c r="L45" t="n">
-        <v>6.76</v>
+        <v>11.12</v>
       </c>
       <c r="M45" t="n">
         <v>2.88</v>
       </c>
       <c r="N45" t="n">
-        <v>6.45</v>
+        <v>12.68</v>
       </c>
       <c r="O45" t="n">
         <v>-1.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>18.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H46" t="n">
-        <v>1149.15</v>
+        <v>1080.7</v>
       </c>
       <c r="I46" t="n">
         <v>1139.578503951191</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K46" t="n">
-        <v>1.56</v>
+        <v>-4.49</v>
       </c>
       <c r="L46" t="n">
         <v>10.3</v>
@@ -3063,7 +3614,7 @@
         <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>3.55</v>
+        <v>5.96</v>
       </c>
       <c r="O46" t="n">
         <v>12.68</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>20.59</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H47" t="n">
-        <v>1236.3</v>
+        <v>1297.25</v>
       </c>
       <c r="I47" t="n">
         <v>1257.409145531444</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-14.4</v>
+        <v>-20.04</v>
       </c>
       <c r="L47" t="n">
-        <v>17.89</v>
+        <v>24.13</v>
       </c>
       <c r="M47" t="n">
         <v>2.8</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>15.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H48" t="n">
-        <v>1450.45</v>
+        <v>1401.05</v>
       </c>
       <c r="I48" t="n">
         <v>1415.101424084352</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K48" t="n">
-        <v>11.81</v>
+        <v>8</v>
       </c>
       <c r="L48" t="n">
         <v>14.66</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>12.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44858</v>
+        <v>44859</v>
       </c>
       <c r="H49" t="n">
-        <v>1532.45</v>
+        <v>1630.35</v>
       </c>
       <c r="I49" t="n">
         <v>1538.413975558016</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K49" t="n">
-        <v>-9.380000000000001</v>
+        <v>-16.37</v>
       </c>
       <c r="L49" t="n">
-        <v>12.06</v>
+        <v>18.1</v>
       </c>
       <c r="M49" t="n">
         <v>2.33</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>6.39</v>
       </c>
       <c r="O49" t="n">
         <v>-3.41</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>12.67</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H50" t="n">
-        <v>1477.2</v>
+        <v>1462.55</v>
       </c>
       <c r="I50" t="n">
         <v>1472.540161324783</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K50" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.29</v>
       </c>
       <c r="L50" t="n">
-        <v>10.11</v>
+        <v>11.49</v>
       </c>
       <c r="M50" t="n">
         <v>0.4</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.91</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H51" t="n">
-        <v>1550.55</v>
+        <v>1573.2</v>
       </c>
       <c r="I51" t="n">
         <v>1568.174349482352</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.02</v>
+        <v>-7.57</v>
       </c>
       <c r="L51" t="n">
-        <v>7.34</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>1.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45138</v>
+        <v>45139</v>
       </c>
       <c r="H52" t="n">
-        <v>2429.55</v>
+        <v>2270.35</v>
       </c>
       <c r="I52" t="n">
         <v>2341.088422839845</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K52" t="n">
-        <v>54.43</v>
+        <v>44.31</v>
       </c>
       <c r="L52" t="n">
         <v>1.98</v>
       </c>
       <c r="M52" t="n">
-        <v>2.84</v>
+        <v>5.33</v>
       </c>
       <c r="N52" t="n">
-        <v>4.38</v>
+        <v>6.55</v>
       </c>
       <c r="O52" t="n">
         <v>1.46</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>16.05</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45160</v>
+        <v>45161</v>
       </c>
       <c r="H53" t="n">
-        <v>2545.55</v>
+        <v>2580</v>
       </c>
       <c r="I53" t="n">
         <v>2573.086186560459</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.12</v>
+        <v>-13.64</v>
       </c>
       <c r="L53" t="n">
-        <v>12.85</v>
+        <v>14.23</v>
       </c>
       <c r="M53" t="n">
         <v>2.26</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>10.74</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45191</v>
+        <v>45194</v>
       </c>
       <c r="H54" t="n">
-        <v>2479.7</v>
+        <v>2415.35</v>
       </c>
       <c r="I54" t="n">
         <v>2474.853693568861</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.89</v>
+        <v>-6.38</v>
       </c>
       <c r="L54" t="n">
-        <v>5.76</v>
+        <v>8.41</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7</v>
+        <v>1.96</v>
       </c>
       <c r="N54" t="n">
         <v>3.65</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.88</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45198</v>
+        <v>45202</v>
       </c>
       <c r="H55" t="n">
-        <v>2653.2</v>
+        <v>2700.6</v>
       </c>
       <c r="I55" t="n">
         <v>2678.249391770472</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.85</v>
+        <v>-11.81</v>
       </c>
       <c r="L55" t="n">
-        <v>10.58</v>
+        <v>12.82</v>
       </c>
       <c r="M55" t="n">
         <v>0.86</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>12.35</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H56" t="n">
-        <v>2545.9</v>
+        <v>2450.1</v>
       </c>
       <c r="I56" t="n">
         <v>2499.56561598565</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.73</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>6.45</v>
+        <v>12.74</v>
       </c>
       <c r="M56" t="n">
         <v>2.49</v>
       </c>
       <c r="N56" t="n">
-        <v>3.17</v>
+        <v>3.76</v>
       </c>
       <c r="O56" t="n">
         <v>1.79</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.16</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H57" t="n">
-        <v>2666.4</v>
+        <v>2722.75</v>
       </c>
       <c r="I57" t="n">
         <v>2679.229377161982</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.83</v>
+        <v>-11.13</v>
       </c>
       <c r="L57" t="n">
-        <v>9.18</v>
+        <v>15.1</v>
       </c>
       <c r="M57" t="n">
         <v>2.06</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>10.24</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="H58" t="n">
-        <v>3148.2</v>
+        <v>2980.95</v>
       </c>
       <c r="I58" t="n">
         <v>3021.391324953795</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K58" t="n">
-        <v>15.63</v>
+        <v>9.48</v>
       </c>
       <c r="L58" t="n">
         <v>3.42</v>
       </c>
       <c r="M58" t="n">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.96</v>
+        <v>5.31</v>
       </c>
       <c r="O58" t="n">
         <v>2.11</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>13.85</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45353</v>
+        <v>45355</v>
       </c>
       <c r="H59" t="n">
-        <v>3214.15</v>
+        <v>3420.4</v>
       </c>
       <c r="I59" t="n">
         <v>3393.782296697815</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.82</v>
+        <v>-14.74</v>
       </c>
       <c r="L59" t="n">
-        <v>13.33</v>
+        <v>15.57</v>
       </c>
       <c r="M59" t="n">
         <v>1.98</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>12.48</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H60" t="n">
-        <v>3266.75</v>
+        <v>3005.55</v>
       </c>
       <c r="I60" t="n">
         <v>3075.687244887912</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.49</v>
+        <v>-12.13</v>
       </c>
       <c r="L60" t="n">
-        <v>6.26</v>
+        <v>13.75</v>
       </c>
       <c r="M60" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N60" t="n">
-        <v>2.57</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
         <v>6.42</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>17.63</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="H61" t="n">
-        <v>3422.95</v>
+        <v>3473.85</v>
       </c>
       <c r="I61" t="n">
         <v>3472.267802464522</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-13.89</v>
+        <v>-15.58</v>
       </c>
       <c r="L61" t="n">
-        <v>15.54</v>
+        <v>16.78</v>
       </c>
       <c r="M61" t="n">
         <v>0.58</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.09</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H62" t="n">
-        <v>4266</v>
+        <v>4011.85</v>
       </c>
       <c r="I62" t="n">
         <v>4184.71127383009</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K62" t="n">
-        <v>22.8</v>
+        <v>15.49</v>
       </c>
       <c r="L62" t="n">
         <v>3.22</v>
@@ -3975,7 +4718,7 @@
         <v>1.57</v>
       </c>
       <c r="N62" t="n">
-        <v>5.44</v>
+        <v>5.96</v>
       </c>
       <c r="O62" t="n">
         <v>1.49</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>16.57</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="H63" t="n">
-        <v>4367.35</v>
+        <v>4709</v>
       </c>
       <c r="I63" t="n">
         <v>4550.360036409617</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.859999999999999</v>
+        <v>-17.38</v>
       </c>
       <c r="L63" t="n">
-        <v>11.67</v>
+        <v>19.14</v>
       </c>
       <c r="M63" t="n">
-        <v>2.53</v>
+        <v>4.18</v>
       </c>
       <c r="N63" t="n">
-        <v>3.72</v>
+        <v>7.82</v>
       </c>
       <c r="O63" t="n">
         <v>-5.96</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.46</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H64" t="n">
-        <v>4225.5</v>
+        <v>4196.8</v>
       </c>
       <c r="I64" t="n">
         <v>4208.317018417149</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K64" t="n">
-        <v>-10.27</v>
+        <v>-10.88</v>
       </c>
       <c r="L64" t="n">
         <v>11.87</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H65" t="n">
-        <v>4528.8</v>
+        <v>4575.95</v>
       </c>
       <c r="I65" t="n">
         <v>4547.318648808403</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.91</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>8.49</v>
+        <v>9.75</v>
       </c>
       <c r="M65" t="n">
         <v>0.91</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.85</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="H66" t="n">
-        <v>4384.8</v>
+        <v>4144.55</v>
       </c>
       <c r="I66" t="n">
         <v>4193.976265815127</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.18</v>
+        <v>-9.43</v>
       </c>
       <c r="L66" t="n">
-        <v>9.279999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="M66" t="n">
         <v>2.15</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>17.37</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H67" t="n">
-        <v>4071.4</v>
+        <v>4319.75</v>
       </c>
       <c r="I67" t="n">
         <v>4179.121911565661</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>1.76</v>
+        <v>-4.23</v>
       </c>
       <c r="L67" t="n">
         <v>6.65</v>
       </c>
       <c r="M67" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="N67" t="n">
-        <v>5.37</v>
+        <v>6.1</v>
       </c>
       <c r="O67" t="n">
         <v>-5.48</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>12.65</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H68" t="n">
-        <v>4177.05</v>
+        <v>3994.45</v>
       </c>
       <c r="I68" t="n">
         <v>4153.898514836493</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.3</v>
+        <v>-7.53</v>
       </c>
       <c r="L68" t="n">
-        <v>4.74</v>
+        <v>8.52</v>
       </c>
       <c r="M68" t="n">
         <v>1.45</v>
       </c>
       <c r="N68" t="n">
-        <v>2.54</v>
+        <v>4.37</v>
       </c>
       <c r="O68" t="n">
         <v>6.1</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>11.02</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H69" t="n">
-        <v>4127.55</v>
+        <v>4480.6</v>
       </c>
       <c r="I69" t="n">
         <v>4362.766361368705</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.33</v>
+        <v>-12.17</v>
       </c>
       <c r="L69" t="n">
-        <v>5.1</v>
+        <v>14.48</v>
       </c>
       <c r="M69" t="n">
         <v>0.86</v>
       </c>
       <c r="N69" t="n">
-        <v>2.31</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O69" t="n">
         <v>-4.37</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>14.78</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45695</v>
+        <v>45698</v>
       </c>
       <c r="H70" t="n">
-        <v>3912.25</v>
+        <v>3794.9</v>
       </c>
       <c r="I70" t="n">
         <v>3818.190168925569</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K70" t="n">
-        <v>-12.68</v>
+        <v>-15.3</v>
       </c>
       <c r="L70" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="M70" t="n">
         <v>1.67</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>12.77</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H71" t="n">
-        <v>2896.1</v>
+        <v>2955.6</v>
       </c>
       <c r="I71" t="n">
         <v>2938.6110812079</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K71" t="n">
-        <v>23.68</v>
+        <v>22.12</v>
       </c>
       <c r="L71" t="n">
         <v>3.62</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>13.25</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H72" t="n">
-        <v>4143.8</v>
+        <v>4081.2</v>
       </c>
       <c r="I72" t="n">
         <v>4082.121231484492</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K72" t="n">
-        <v>40.2</v>
+        <v>38.08</v>
       </c>
       <c r="L72" t="n">
         <v>2.46</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>7</v>
+      </c>
+      <c r="U72" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>10.29</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="H73" t="n">
-        <v>4086.8</v>
+        <v>4284.4</v>
       </c>
       <c r="I73" t="n">
         <v>4200.81472087027</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.14</v>
+        <v>-4.98</v>
       </c>
       <c r="L73" t="n">
-        <v>3.06</v>
+        <v>5.27</v>
       </c>
       <c r="M73" t="n">
         <v>0.67</v>
       </c>
       <c r="N73" t="n">
-        <v>2.77</v>
+        <v>4.84</v>
       </c>
       <c r="O73" t="n">
         <v>-1.51</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>9.56</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H74" t="n">
-        <v>4318.4</v>
+        <v>4069.9</v>
       </c>
       <c r="I74" t="n">
         <v>4259.229617970405</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K74" t="n">
-        <v>0.79</v>
+        <v>-5.01</v>
       </c>
       <c r="L74" t="n">
-        <v>4.58</v>
+        <v>5.47</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="N74" t="n">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="O74" t="n">
         <v>4.84</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>12.18</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H75" t="n">
-        <v>4079.8</v>
+        <v>4367</v>
       </c>
       <c r="I75" t="n">
         <v>4238.353311653414</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.24</v>
+        <v>-7.3</v>
       </c>
       <c r="L75" t="n">
-        <v>6.11</v>
+        <v>12.04</v>
       </c>
       <c r="M75" t="n">
-        <v>1.29</v>
+        <v>5.4</v>
       </c>
       <c r="N75" t="n">
-        <v>3.25</v>
+        <v>7.04</v>
       </c>
       <c r="O75" t="n">
         <v>-5.75</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>11.24</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="H76" t="n">
-        <v>4789.5</v>
+        <v>4537</v>
       </c>
       <c r="I76" t="n">
         <v>4596.444763894004</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>9.67</v>
+        <v>3.89</v>
       </c>
       <c r="L76" t="n">
         <v>1.94</v>
@@ -4773,7 +5684,7 @@
         <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>4.36</v>
+        <v>5.27</v>
       </c>
       <c r="O76" t="n">
         <v>7.04</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>15.92</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H77" t="n">
-        <v>4458.7</v>
+        <v>4598.5</v>
       </c>
       <c r="I77" t="n">
         <v>4580.344672607735</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K77" t="n">
-        <v>1.73</v>
+        <v>-1.36</v>
       </c>
       <c r="L77" t="n">
         <v>7.24</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>12.56</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H78" t="n">
-        <v>5251</v>
+        <v>5106</v>
       </c>
       <c r="I78" t="n">
         <v>5153.012339556178</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K78" t="n">
-        <v>14.19</v>
+        <v>11.04</v>
       </c>
       <c r="L78" t="n">
         <v>1.38</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>12.48</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H79" t="n">
-        <v>5023.3</v>
+        <v>5500</v>
       </c>
       <c r="I79" t="n">
         <v>5173.367820128606</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K79" t="n">
-        <v>1.62</v>
+        <v>-7.72</v>
       </c>
       <c r="L79" t="n">
-        <v>3.4</v>
+        <v>7.91</v>
       </c>
       <c r="M79" t="n">
-        <v>0.77</v>
+        <v>3.54</v>
       </c>
       <c r="N79" t="n">
-        <v>4.16</v>
+        <v>9.49</v>
       </c>
       <c r="O79" t="n">
         <v>-2.76</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>12</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H80" t="n">
-        <v>5740.3</v>
+        <v>5348</v>
       </c>
       <c r="I80" t="n">
         <v>5350.288981402689</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K80" t="n">
-        <v>4.37</v>
+        <v>-2.76</v>
       </c>
       <c r="L80" t="n">
         <v>5.44</v>
       </c>
       <c r="M80" t="n">
-        <v>0.93</v>
+        <v>2.88</v>
       </c>
       <c r="N80" t="n">
-        <v>2.6</v>
+        <v>6.83</v>
       </c>
       <c r="O80" t="n">
         <v>9.49</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>39</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.12</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.49</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.43</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143.1</v>
+        <v>121.93</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.890000000000001</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.24</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.43</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.51</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="25">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.45</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="27">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
